--- a/nr-update-patient-identifiers/ig/StructureDefinition-fr-core-address-insee-code.xlsx
+++ b/nr-update-patient-identifiers/ig/StructureDefinition-fr-core-address-insee-code.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-11T15:02:05+00:00</t>
+    <t>2025-07-11T15:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-patient-identifiers/ig/StructureDefinition-fr-core-address-insee-code.xlsx
+++ b/nr-update-patient-identifiers/ig/StructureDefinition-fr-core-address-insee-code.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-11T15:14:34+00:00</t>
+    <t>2025-07-15T08:52:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-patient-identifiers/ig/StructureDefinition-fr-core-address-insee-code.xlsx
+++ b/nr-update-patient-identifiers/ig/StructureDefinition-fr-core-address-insee-code.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-15T08:52:52+00:00</t>
+    <t>2025-07-17T15:24:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-patient-identifiers/ig/StructureDefinition-fr-core-address-insee-code.xlsx
+++ b/nr-update-patient-identifiers/ig/StructureDefinition-fr-core-address-insee-code.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-17T15:24:19+00:00</t>
+    <t>2025-07-19T09:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
